--- a/data_extactor/batch_10_fa/trimmed/batch_0065_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0065_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | زبان انگلیسی | اداری | رایانه و الکترونیک | پرسنلی و منابع انسانی | اقتصاد و حسابداری</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | پرسنل و منابع انسانی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | سرپرستان رده‌اول کارکنان تهیه و سرو غذا | سرپرستان رده‌اول ارائه‌دهندگان خدمات فردی | سرپرستان رده‌اول کارکنان فروش خرده‌فروشی | کارشناسان منابع انسانی | تحلیل‌گران مدیریت و فرآیندها | کارمندان امور اداری و دفتری عمومی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | کارشناسان منابع انسانی | کارشناسان تحلیل مدیریت و روش‌ها | متصدیان امور دفتری و امور عمومی اداری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | اداری | رایانه و الکترونیک | مخابرات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | مخابرات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | دید نزدیک | توجه انتخابی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | توجه انتخابی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارشناسان خدمات مشتریان | کاربران ورود اطلاعات | مسئولان دفاتر و دستیاران اجرایی مدیریت | کارمندان امور اداری و دفتری عمومی | متصدیان پذیرش و کارمندان پذیرش و اطلاعات | اپراتورهای تلفن | تایپیست‌ها و کاربران پردازش متن</t>
+          <t>کارشناسان خدمات و پشتیبانی مشتریان | متصدیان ورود اطلاعات و داده‌آمایی | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان امور دفتری و امور عمومی اداری | متصدیان پذیرش و اطلاعات | اپراتورهای تلفن | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مخابرات | اداری | زبان انگلیسی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | مخابرات | اداری | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | دید نزدیک | توجه انتخابی | حساسیت به مسئله</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | توجه انتخابی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارشناسان خدمات مشتریان | کاربران ورود اطلاعات | کارمندان امور اداری و دفتری عمومی | متصدیان پذیرش و کارمندان پذیرش و اطلاعات | منشی‌ها و مسئولان دفاتر اداری، به‌جز حقوقی، پزشکی و اجرایی | اپراتورهای مراکز تلفن و پاسخگویی | بازاریابان تلفنی</t>
+          <t>کارشناسان خدمات و پشتیبانی مشتریان | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان امور دفتری و امور عمومی اداری | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | اپراتورهای مراکز تلفن و پاسخگویی | کارشناسان بازاریابی تلفنی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مخابرات | خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | ارتباطات و رسانه | ایمنی و امنیت عمومی</t>
+          <t>مخابرات | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | ارتباطات و رسانه | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورهای مراکز تلفن و پاسخگویی | اپراتورهای تلفن | اپراتورهای مخابراتی فوریت‌های عمومی و ایمنی | کارشناسان خدمات مشتریان | متصدیان پذیرش و کارمندان پذیرش و اطلاعات | کاربران ورود اطلاعات | کارمندان امور اداری و دفتری عمومی</t>
+          <t>اپراتورهای مراکز تلفن و پاسخگویی | اپراتورهای تلفن | اپراتورهای فوریت‌های پلیسی و امدادی | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان پذیرش و اطلاعات | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان امور دفتری و امور عمومی اداری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات | اقتصاد و حسابداری | حقوق و امور دولتی | رایانه و الکترونیک | اداری</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | اقتصاد و حسابداری | قانون و دولت | رایانه و الکترونیک | اداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | دید نزدیک</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران اعتباری | مشاوران اعتباری | کارشناسان خدمات مشتریان | کارشناسان تسهیلات و اعتبارات | تحویل‌داران و متصدیان باجه بانک</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران اعتبارات و تسهیلات | مشاوران اعتباری و مدیریت بدهی | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان و مسئولان تسهیلات و اعتبارات | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | ریاضیات | شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | نگارش</t>
+          <t>درک مطلب | ریاضیات | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>اداری | خدمات مشتریان و خدمات فردی | زبان انگلیسی | اقتصاد و حسابداری | ریاضیات | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>اداری | خدمات مشتری و شخصی | زبان انگلیسی | اقتصاد و حسابداری | ریاضیات | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات | بیان شفاهی | بیان کتبی | درک شفاهی | توانایی محاسبات عددی</t>
+          <t>بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | بیان کتبی | درک شفاهی | توانایی عددی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان خدمات مشتریان | کارمندان امور اداری و دفتری عمومی | کارمندان امور حقوق، دستمزد و ثبت زمان | کارمندان انبار، بارگیری، تحویل و موجودی کالا</t>
+          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان امور دفتری و امور عمومی اداری | کارمندان امور حقوق، دستمزد و ثبت زمان | کارمندان انبار، ارسال و دریافت کالا</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | سخن گفتن | نظارت</t>
+          <t>ریاضیات | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | اداری | ریاضیات | زبان انگلیسی | اقتصاد و حسابداری | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | اداری | ریاضیات | زبان انگلیسی | اقتصاد و حسابداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | استدلال ریاضی | دید نزدیک | درک کتبی | بیان کتبی | توانایی محاسبات عددی | حساسیت به مسئله</t>
+          <t>درک شفاهی | استدلال ریاضی | بینایی نزدیک | درک کتبی | بیان کتبی | توانایی عددی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارشناسان تأیید، اعتبارسنجی و امور اعتبار | کارمندان افتتاح حساب | کارمندان امور حقوق، دستمزد و ثبت زمان | ممیزان و مأموران وصول مالیات و کارشناسان امور مالیاتی</t>
+          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | متصدیان افتتاح حساب | کارمندان امور حقوق، دستمزد و ثبت زمان | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Office software | Microsoft Word | Microsoft Outlook | سامانه‌های ثبت تراکنش‌های صندوق | نرم‌افزارهای مدیریت اسناد مالی</t>
+          <t>Corel WordPerfect Office Suite | Microsoft Office software | نرم‌افزار Microsoft Office | Microsoft Outlook | سامانه‌های ثبت تراکنش‌های صندوق | نرم‌افزارهای مدیریت اسناد مالی</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | ریاضیات | نظارت | تفکر انتقادی | نگارش | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | ریاضیات | نظارت | تفکر انتقادی | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | اداری</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | حساسیت به مسئله | استدلال ریاضی | توانایی محاسبات عددی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | حساسیت به مسئله | استدلال ریاضی | توانایی عددی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | صندوق‌داران | سرپرستان رده‌اول کارکنان خدمات مراکز تفریحی و بازی | مسئولان خرد کردن پول و صندوق‌داران باجه‌های بازی | کارمندان افتتاح حساب | تحویل‌داران و متصدیان باجه بانک</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | صندوق‌داران | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | صندوق‌داران و متصدیان تبدیل ژتون و وجه در مراکز تفریحی | متصدیان افتتاح حساب | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | ریاضیات | نگارش | سخن گفتن | تفکر انتقادی | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | ریاضیات | نگارش | سخن گفتن | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>اداری | ریاضیات | اقتصاد و حسابداری | پرسنلی و منابع انسانی | مدیریت و امور اداری | رایانه و الکترونیک</t>
+          <t>اداری | ریاضیات | اقتصاد و حسابداری | پرسنل و منابع انسانی | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان کتبی | دید نزدیک | استدلال ریاضی | توانایی محاسبات عددی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان کتبی | بینایی نزدیک | استدلال ریاضی | توانایی عددی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارمندان دفترداری، حسابداری و امور حسابرسی | مدیران حقوق و مزایا | کارشناسان جبران خدمت، مزایا و تجزیه‌وتحلیل شغل | دستیاران منابع انسانی، به‌جز امور حقوق و دستمزد و ثبت زمان | کارشناسان منابع انسانی | کارمندان امور اداری و دفتری عمومی</t>
+          <t>حسابداران و حسابرسان | کارمندان دفترداری، حسابداری و امور حسابرسی | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان منابع انسانی | متصدیان امور دفتری و امور عمومی اداری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>اداری | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | مدیریت و امور اداری | ریاضیات | ترابری و حمل‌ونقل</t>
+          <t>اداری | خدمات مشتری و شخصی | اقتصاد و حسابداری | مدیریت و اداره | ریاضیات | حمل و نقل</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | دید نزدیک | بیان کتبی | مرتب‌سازی اطلاعات | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارمندان پیشخوان و کرایه کالا | متخصصان لجستیک و زنجیره تأمین | کارمندان ثبت و پیگیری سفارش‌ها | کارمندان برنامه‌ریزی تولید و تسریع در سفارش‌ها | مأموران خرید، به‌جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید و تدارکات | کارمندان انبار، بارگیری، تحویل و موجودی کالا</t>
+          <t>متصدیان باجه و کرایه کالا و خدمات | کارشناسان لجستیک و مدیریت زنجیره تأمین | متصدیان ثبت و پیگیری سفارش‌ها | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | کارمندان انبار، ارسال و دریافت کالا</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
